--- a/registration_forms/012_registration_anomaly_review_form--registration_forms.xlsx
+++ b/registration_forms/012_registration_anomaly_review_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Registration Anomaly Review Form</t>
+          <t>Registration Anomaly Review Form Title</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -589,35 +589,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>form_id</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Form ID</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_ids</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Form IDs</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,23 +630,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_ids</t>
+          <t>output_file</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Form IDs</t>
+          <t>Output File</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>assigned_tool</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Assigned Tool</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,69 +676,69 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>review_status</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Review Status</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>review_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Review Date</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>review_time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Review Time</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>reviewer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Reviewer</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>reviewer_comment</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Reviewer Comment</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,18 +796,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>action_taken</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Action Taken</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,18 +819,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>follow_up</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Follow-up</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,18 +842,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>review_notes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Review Notes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,18 +865,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>next_steps</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Next Steps</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>reviewer_id</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Reviewer ID</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,179 +911,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>reviewer_email</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Reviewer's Email</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>form_title</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>form_category</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_ids</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Form IDs</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>form_title</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>form_description</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1165,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20498</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20498</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1021,80 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>66618</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>66618</t>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>form_ids_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>review_status_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>review_status_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>review_status_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
